--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -755,16 +755,16 @@
         <v>0.8349514563106796</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
         <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8629810544129037</v>
+        <v>0.8529779922510174</v>
       </c>
     </row>
     <row r="15">
@@ -777,16 +777,16 @@
         <v>0.5715909090909091</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="D15" t="n">
         <v>0.5891304347826087</v>
       </c>
       <c r="E15" t="n">
-        <v>0.649812734082397</v>
+        <v>0.6329588014981273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5968642887197479</v>
+        <v>0.583035420958296</v>
       </c>
     </row>
     <row r="16">
@@ -799,16 +799,16 @@
         <v>0.5839866951770016</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6026070763500931</v>
+        <v>0.5380952380952381</v>
       </c>
       <c r="D16" t="n">
         <v>0.6083916083916083</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6804716709807306</v>
+        <v>0.6429292929292929</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6188642627248584</v>
+        <v>0.5933507086482852</v>
       </c>
     </row>
     <row r="17">
@@ -821,16 +821,16 @@
         <v>0.8129920397114829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8485016030255909</v>
+        <v>0.8273932253313697</v>
       </c>
       <c r="D17" t="n">
         <v>0.8016983016983018</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8782465822078326</v>
+        <v>0.8558555855585559</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8353596316608021</v>
+        <v>0.8244847880749276</v>
       </c>
     </row>
     <row r="18">
@@ -843,16 +843,16 @@
         <v>0.7276515151515153</v>
       </c>
       <c r="C18" t="n">
-        <v>0.646978021978022</v>
+        <v>0.6936813186813187</v>
       </c>
       <c r="D18" t="n">
         <v>0.621195652173913</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7359550561797752</v>
+        <v>0.7008426966292136</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6829450613708063</v>
+        <v>0.6858427956589901</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +868,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [11, 2]]</t>
+          <t>[[84, 0], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86, 3], [8, 4]]</t>
+          <t>[[83, 6], [8, 4]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [12, 3]]</t>
+          <t>[[85, 3], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8629810544129037</v>
+        <v>0.8529779922510174</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02595644158181611</v>
+        <v>0.01678182514237675</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5968642887197479</v>
+        <v>0.583035420958296</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03122397319699055</v>
+        <v>0.03408555768489376</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6188642627248584</v>
+        <v>0.5933507086482852</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03669431177876421</v>
+        <v>0.03816122527752064</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8353596316608021</v>
+        <v>0.8244847880749276</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0301885584412039</v>
+        <v>0.02027247622005692</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6829450613708063</v>
+        <v>0.6858427956589901</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04978791022462441</v>
+        <v>0.039413391311434</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [12, 3]]</t>
+          <t>[[85, 3], [12, 3]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,7 +613,7 @@
         <v>0.8058252427184466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7938144329896907</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="D8" t="n">
         <v>0.7410714285714286</v>
@@ -622,7 +622,7 @@
         <v>0.8118811881188119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7881480730995944</v>
+        <v>0.8010346710377387</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         <v>0.8310606060606061</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7834249084249085</v>
+        <v>0.7806776556776557</v>
       </c>
       <c r="D9" t="n">
         <v>0.725</v>
@@ -644,7 +644,7 @@
         <v>0.8211610486891385</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7901616407936632</v>
+        <v>0.7894748276068501</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>0.7201086956521738</v>
       </c>
       <c r="C10" t="n">
-        <v>0.685064935064935</v>
+        <v>0.7261434217955958</v>
       </c>
       <c r="D10" t="n">
         <v>0.65878768778233</v>
@@ -666,7 +666,7 @@
         <v>0.6981280478212993</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6905223415801846</v>
+        <v>0.7007919632628498</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +679,7 @@
         <v>0.8298860278598565</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8205248359887536</v>
+        <v>0.8584002281895604</v>
       </c>
       <c r="D11" t="n">
         <v>0.7665045848153317</v>
@@ -688,7 +688,7 @@
         <v>0.8394021091585326</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8140793894556186</v>
+        <v>0.8235482375058203</v>
       </c>
     </row>
     <row r="12">
@@ -701,7 +701,7 @@
         <v>0.9212121212121213</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8663003663003663</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="D12" t="n">
         <v>0.8358695652173913</v>
@@ -710,7 +710,7 @@
         <v>0.8529962546816479</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8690945768528817</v>
+        <v>0.8695524523107572</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[67, 17], [3, 10]]</t>
+          <t>[[73, 11], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[70, 19], [3, 12]]</t>
+          <t>[[71, 17], [4, 12]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7881480730995944</v>
+        <v>0.8010346710377387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0279466508220773</v>
+        <v>0.03775246634038983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7901616407936632</v>
+        <v>0.7894748276068501</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04160862784239369</v>
+        <v>0.04173663619940334</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6905223415801846</v>
+        <v>0.7007919632628498</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02219273897157369</v>
+        <v>0.02639738720054234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8140793894556186</v>
+        <v>0.8235482375058203</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02826656933715006</v>
+        <v>0.03449692884825035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8690945768528817</v>
+        <v>0.8695524523107572</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03196522883367333</v>
+        <v>0.03193502784281874</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[70, 19], [3, 12]]</t>
+          <t>[[71, 17], [4, 12]]</t>
         </is>
       </c>
     </row>
